--- a/output/pdf_financials_xlsx/BIRD.xlsx
+++ b/output/pdf_financials_xlsx/BIRD.xlsx
@@ -2264,13 +2264,13 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.145336</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.147822</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.147822</v>
       </c>
     </row>
     <row r="93">
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.130271</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0.836656</v>
@@ -3532,7 +3532,11 @@
           <t>Share-based payment reserve 5</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3858,7 +3862,11 @@
           <t>Share-based payment reserve 4</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -4802,7 +4810,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BIRD.xlsx
+++ b/output/pdf_financials_xlsx/BIRD.xlsx
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.011359</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.010541</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000453</v>
       </c>
     </row>
     <row r="13">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.39651</v>
+        <v>-0.407869</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.111237</v>
+        <v>-1.121778</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.299342</v>
+        <v>-0.299795</v>
       </c>
     </row>
     <row r="28">
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.39651</v>
+        <v>-0.407869</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.111237</v>
+        <v>-1.121778</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.299342</v>
+        <v>-0.299795</v>
       </c>
     </row>
     <row r="30">
@@ -1125,16 +1125,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.5040790000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.102676</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.148683</v>
       </c>
     </row>
     <row r="35">
@@ -1163,16 +1163,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.5040790000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.102676</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.148683</v>
       </c>
     </row>
     <row r="37">
@@ -1391,16 +1391,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.512967</v>
+        <v>0.008888</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.110418</v>
+        <v>0.007742</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.151702</v>
+        <v>0.003019</v>
       </c>
     </row>
     <row r="49">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">

--- a/output/pdf_financials_xlsx/BIRD.xlsx
+++ b/output/pdf_financials_xlsx/BIRD.xlsx
@@ -2425,10 +2425,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003803</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>7.8e-05</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.015504</v>
+        <v>0.011701</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.002099</v>
+        <v>0.002177</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.071618</v>
@@ -4776,7 +4776,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -5024,7 +5028,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
